--- a/AAII_Financials/Quarterly/HLDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="92">
   <si>
     <t>HLDCY</t>
   </si>
@@ -656,93 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,8 +805,14 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +867,14 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +929,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +957,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1015,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1077,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1099,8 +1139,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1143,11 +1189,11 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1155,8 +1201,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,8 +1226,10 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1230,8 +1284,14 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1286,8 +1346,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1374,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1364,8 +1432,14 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1420,8 +1494,14 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,8 +1556,14 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1532,8 +1618,14 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1588,8 +1680,14 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,8 +1742,14 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1700,8 +1804,14 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1756,8 +1866,14 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1928,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1856,11 +1978,11 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -1868,8 +1990,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +2052,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2114,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2036,8 +2176,14 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2092,8 +2238,14 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,8 +2300,14 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2204,69 +2362,81 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2457,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,512 +2481,568 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2738700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2739400</v>
+      </c>
+      <c r="F41" s="3">
         <v>2852000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2853000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2114700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2133600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2306900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2306300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1931200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1926800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2768000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2761300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1700300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1697300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1448600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>115300</v>
+      </c>
+      <c r="F42" s="3">
         <v>118500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>118500</v>
       </c>
-      <c r="F42" s="3">
-        <v>257700</v>
-      </c>
-      <c r="G42" s="3">
-        <v>260000</v>
-      </c>
       <c r="H42" s="3">
+        <v>133400</v>
+      </c>
+      <c r="I42" s="3">
+        <v>134600</v>
+      </c>
+      <c r="J42" s="3">
         <v>116900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>116900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>102100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>101800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>77300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>77100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>67900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>67800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>64500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>975100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>975400</v>
+      </c>
+      <c r="F43" s="3">
         <v>870100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>870400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>985100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>993900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1146700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1146400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1065700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1063300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1293500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1290400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1176000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1174000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1124600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9376800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>9379300</v>
+      </c>
+      <c r="F44" s="3">
         <v>10229500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10233200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>10730500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>10826700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>11021300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>11018500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>11586100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>11559900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>12054000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>12024800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>12898300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>12876100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>12473300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>64700</v>
+      </c>
+      <c r="F45" s="3">
         <v>85600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>85600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>52000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>52400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>47500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>47500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>56700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>56600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>346700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>345800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>114600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>114400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>51400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13967600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13971200</v>
+      </c>
+      <c r="F46" s="3">
         <v>14773800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>14779100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14605700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>14736700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>15319300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>15315500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>15473100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>15438100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17171600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17130000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>16657100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>16628400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>16001200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17079700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>17084200</v>
+      </c>
+      <c r="F47" s="3">
         <v>17247800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>17254000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>16529700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>16677900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>16584100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>16579900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>16588300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>16550900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>16803700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>16763000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>16398300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>16370000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>16823100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36660200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>36669800</v>
+      </c>
+      <c r="F48" s="3">
         <v>36379700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>36392700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>35798700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>36119700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>35692800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>35683900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>35453900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>35373800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>34578600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>34494900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>34034600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>33976000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>34047600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>44800</v>
+      </c>
+      <c r="F49" s="3">
         <v>45400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>45400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>45100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>45500</v>
-      </c>
-      <c r="H49" s="3">
-        <v>45800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>45800</v>
       </c>
       <c r="J49" s="3">
         <v>45800</v>
       </c>
       <c r="K49" s="3">
+        <v>45800</v>
+      </c>
+      <c r="L49" s="3">
+        <v>45800</v>
+      </c>
+      <c r="M49" s="3">
         <v>45700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>46100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>46000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>46200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>46100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>46700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +3097,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,64 +3159,76 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>575900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>576000</v>
+      </c>
+      <c r="F52" s="3">
         <v>34800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>34800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>640400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>646100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>66200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>66200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>80400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>80200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>95100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>94900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>127700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>127500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>155800</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,64 +3283,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68524600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>68542500</v>
+      </c>
+      <c r="F54" s="3">
         <v>69298500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>69323400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>67843900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>68452200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>68392700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>68375500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>68510500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>68355800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>69452200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>69283900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>68082300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>67964900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>67945300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3373,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,29 +3397,31 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="D57" s="3">
+        <v>718800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>719000</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>991300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000200</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,288 +3455,324 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1347700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1348100</v>
+      </c>
+      <c r="F58" s="3">
         <v>1603400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1604000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1616300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1630800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2449600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2449000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3315000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3307500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4326100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4315600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3767500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>3761000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>4646000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1518900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1519300</v>
+      </c>
+      <c r="F59" s="3">
         <v>2086400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2087100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1081200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1090800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2319000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2318400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2709600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2703400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2161100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2155800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2184400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2180600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1984500</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4689700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4690900</v>
+      </c>
+      <c r="F60" s="3">
         <v>4766000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4767700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4745400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4787900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>5897800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5896300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7205400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7189200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7697800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7679100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7449700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7436900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>7755800</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18859200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>18864200</v>
+      </c>
+      <c r="F61" s="3">
         <v>19563800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>19570900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>18756900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>18925100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>17405500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>17401100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>16361500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>16324600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>16372600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>16332900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>15701800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>15674700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>14603100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>74400</v>
+      </c>
+      <c r="F62" s="3">
         <v>68000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>68000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>87800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>88600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>130000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>130000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>173800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>173400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>175600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>175200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>192100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>191700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>150300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3827,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3889,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,64 +3951,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24741800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>24748300</v>
+      </c>
+      <c r="F66" s="3">
         <v>25502200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>25511400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>24693400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>24914800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>24546300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24540100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>24866000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>24809800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>25403700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>25342200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>24495300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>24453100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>23679700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +4041,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +4099,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +4161,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4223,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,64 +4285,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>34933400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>34945900</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>35381100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>35372300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>35097100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>35017800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>35480300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>35394400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>35317900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>35257000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>35495100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4409,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4471,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,64 +4533,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41513800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>41524600</v>
+      </c>
+      <c r="F76" s="3">
         <v>41429500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>41444400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>40782200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>41147800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>41473700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>41463300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>41294000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>41200700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>41800900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>41699600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>41379000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>41307700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>42059200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,69 +4657,81 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4396,8 +4786,14 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,64 +4814,72 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>15600</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>15700</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>16900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>16900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>17300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>17300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>17900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>17800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>16400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>16400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>17100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4934,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4996,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +5058,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +5120,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,8 +5182,14 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4771,47 +5205,53 @@
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>463500</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>518500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>556700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>555400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>367600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>367000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>511800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,8 +5272,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4876,11 +5318,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4888,8 +5330,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5392,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,8 +5454,14 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5017,47 +5477,53 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-51800</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-68100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>114200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>114000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-112900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-112700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>373700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5544,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5095,47 +5563,53 @@
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3">
         <v>155800</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3">
         <v>403000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3">
         <v>155000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>154600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>401600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>400900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>155200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5664,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5726,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,8 +5788,14 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5319,103 +5811,115 @@
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-313900</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1045200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-29100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-29100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-316600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-316100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-806900</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-6700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-6700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-19000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-18900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-7500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-7500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5432,42 +5936,48 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>92800</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-595100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>643300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>641700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-68500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-68400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>59600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>
